--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:21:29+00:00</t>
+    <t>2026-06-16T14:47:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T14:47:27+00:00</t>
+    <t>2026-06-16T15:00:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T15:00:27+00:00</t>
+    <t>2026-06-16T15:00:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T15:00:36+00:00</t>
+    <t>2026-06-16T15:13:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T15:13:20+00:00</t>
+    <t>2026-06-16T15:51:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T15:51:38+00:00</t>
+    <t>2026-06-16T16:03:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/all-profiles.xlsx
+++ b/main/ig/all-profiles.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:03:19+00:00</t>
+    <t>2026-06-16T16:17:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
